--- a/usuarios_master.xlsx
+++ b/usuarios_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,65 +432,21 @@
           <t>Telefono</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Contraseña_TOTP</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mario.jafet</t>
+          <t>Mario</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OOJUVXDX2OGPJ62XY7MCCP7W3FBDDT3X</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>user1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>VRFRLX3DZ54BCUUBHJML6WXW2Q6HKF3A</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>VB6YMBFTCMDQAU3NM4D2TZBBRPO4QUEC</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>user.1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>GZZRUTPAKYX563FDKSNX4DSFUDAINCWG</t>
+          <t>5XUAS3ZXOZUWHJLVT2AGXD2FIQTKU2BS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>5528489669</t>
         </is>
       </c>
     </row>

--- a/usuarios_master.xlsx
+++ b/usuarios_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,9 +444,39 @@
           <t>5XUAS3ZXOZUWHJLVT2AGXD2FIQTKU2BS</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>5528489669</t>
+      <c r="C2" t="n">
+        <v>5528489669</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MARIO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>62NQWMP7ACNWTZA5KJZUORY7Z6QOHGV7</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>525528489777</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ebromares1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>JQ2GSZJEQFD6WDC6OUCEYEHMKGR7LYAV</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>+525528489556</t>
         </is>
       </c>
     </row>
